--- a/dataset/processed/coffee_shops.xlsx
+++ b/dataset/processed/coffee_shops.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jempolan Coffee &amp; Eatery</t>
+          <t>ARAH Coffee Pandawa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,17 +482,17 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>
-Jl. Sidoasih No.3A, Tiyosan, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+Kaliurang St No.27, Karang Wuni, Caturtunggal, Depok, Sleman Regency, Special Region of Yogyakarta 55284</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-7.7341524</t>
+          <t>-7.7605444</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>110.399428!15sChhjb2ZmZWUgc2hvcCBkZXBvayBzbGVtYW5aGiIYY29mZmVlIHNob3AgZGVwb2sgc2xlbWFukgELY29mZmVlX3Nob3CaASRDaGREU1VoTk1HOW5TMFZLY2pSeU5sOUtaMkZRZDIxM1JSQULgAQD6AQQIUxA_</t>
+          <t>110.3809541!15sChhjb2ZmZWUgc2hvcCBkZXBvayBzbGVtYW5aGiIYY29mZmVlIHNob3AgZGVwb2sgc2xlbWFukgELY29mZmVlX3Nob3CaASNDaFpEU1VoTk1HOW5TMFZKUTBGblNVUmxMWE5VVm1WUkVBReABAPoBBAgAEEI</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Jempolan+Coffee+%26+Eatery/@-7.7341524,110.3633791,14z/data=!4m10!1m2!2m1!1scoffee+shop+depok+sleman!3m6!1s0x2e7a59f110f9fdab:0x6cc2e4cea03c38e1!8m2!3d-7.7341524!4d110.399428!15sChhjb2ZmZWUgc2hvcCBkZXBvayBzbGVtYW5aGiIYY29mZmVlIHNob3AgZGVwb2sgc2xlbWFukgELY29mZmVlX3Nob3CaASRDaGREU1VoTk1HOW5TMFZLY2pSeU5sOUtaMkZRZDIxM1JSQULgAQD6AQQIUxA_!16s%2Fg%2F11r41m2jlb?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUxMy4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/ARAH+Coffee+Pandawa/@-7.7605444,110.3449052,14z/data=!4m10!1m2!2m1!1scoffee+shop+depok+sleman!3m6!1s0x2e7a5976c286abeb:0x1dbc542ad0bece78!8m2!3d-7.7605444!4d110.3809541!15sChhjb2ZmZWUgc2hvcCBkZXBvayBzbGVtYW5aGiIYY29mZmVlIHNob3AgZGVwb2sgc2xlbWFukgELY29mZmVlX3Nob3CaASNDaFpEU1VoTk1HOW5TMFZKUTBGblNVUmxMWE5VVm1WUkVBReABAPoBBAgAEEI!16s%2Fg%2F11rqwxvq7j?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUxMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
